--- a/VerveStacks_IDN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_IDN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B633FCBE-A6F4-47C1-86A5-0F3A27F3A377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A92EE9EC-722D-4252-97D9-B47A16758D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{46BC4A2E-9908-4632-9AF4-CEB65E5BA299}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0D89265B-3111-4EDC-B670-7EC3D7D3C691}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -31,6 +31,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -68,664 +71,664 @@
     <t>ELC</t>
   </si>
   <si>
-    <t>e_ID1-275</t>
-  </si>
-  <si>
-    <t>e_w721685825-275</t>
-  </si>
-  <si>
-    <t>g_ID1-275-w721685825-275</t>
+    <t>e_ID1-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w721685825-275_IDN</t>
+  </si>
+  <si>
+    <t>g_ID1-275_IDN-w721685825-275_IDN</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>e_ID11-500</t>
-  </si>
-  <si>
-    <t>e_ID10-500</t>
-  </si>
-  <si>
-    <t>g_ID11-500-ID10-500</t>
-  </si>
-  <si>
-    <t>e_ID12-500</t>
-  </si>
-  <si>
-    <t>g_ID12-500-ID10-500</t>
-  </si>
-  <si>
-    <t>e_ID13-500</t>
-  </si>
-  <si>
-    <t>e_ID16-500</t>
-  </si>
-  <si>
-    <t>g_ID13-500-ID16-500</t>
-  </si>
-  <si>
-    <t>e_ID22-500</t>
-  </si>
-  <si>
-    <t>g_ID13-500-ID22-500</t>
-  </si>
-  <si>
-    <t>e_w960747902-500</t>
-  </si>
-  <si>
-    <t>g_ID13-500-w960747902-500</t>
-  </si>
-  <si>
-    <t>e_ID14-500</t>
-  </si>
-  <si>
-    <t>e_ID17-500</t>
-  </si>
-  <si>
-    <t>g_ID14-500-ID17-500</t>
-  </si>
-  <si>
-    <t>e_ID19-500</t>
-  </si>
-  <si>
-    <t>g_ID16-500-ID19-500</t>
-  </si>
-  <si>
-    <t>e_ID18-500</t>
-  </si>
-  <si>
-    <t>e_w662591948-500</t>
-  </si>
-  <si>
-    <t>g_ID18-500-w662591948-500</t>
-  </si>
-  <si>
-    <t>e_ID20-500</t>
-  </si>
-  <si>
-    <t>g_ID20-500-ID19-500</t>
-  </si>
-  <si>
-    <t>e_ID21-500</t>
-  </si>
-  <si>
-    <t>g_ID21-500-ID20-500</t>
-  </si>
-  <si>
-    <t>e_ID25-500</t>
-  </si>
-  <si>
-    <t>g_ID22-500-ID25-500</t>
-  </si>
-  <si>
-    <t>e_w271376037-500</t>
-  </si>
-  <si>
-    <t>g_ID22-500-w271376037-500</t>
-  </si>
-  <si>
-    <t>e_ID26-500</t>
-  </si>
-  <si>
-    <t>e_w264550744-500</t>
-  </si>
-  <si>
-    <t>g_ID26-500-w264550744-500</t>
-  </si>
-  <si>
-    <t>e_ID27-500</t>
-  </si>
-  <si>
-    <t>e_ID28-500</t>
-  </si>
-  <si>
-    <t>g_ID27-500-ID28-500</t>
-  </si>
-  <si>
-    <t>e_ID31-500</t>
-  </si>
-  <si>
-    <t>e_w166633831-500</t>
-  </si>
-  <si>
-    <t>g_ID31-500-w166633831-500</t>
-  </si>
-  <si>
-    <t>e_w689263666-500</t>
-  </si>
-  <si>
-    <t>g_ID31-500-w689263666-500</t>
-  </si>
-  <si>
-    <t>e_ID33-500</t>
-  </si>
-  <si>
-    <t>e_w264410236-500</t>
-  </si>
-  <si>
-    <t>g_ID33-500-w264410236-500</t>
-  </si>
-  <si>
-    <t>e_w314452486-500</t>
-  </si>
-  <si>
-    <t>g_ID33-500-w314452486-500</t>
-  </si>
-  <si>
-    <t>e_ID34-500</t>
-  </si>
-  <si>
-    <t>e_w265568001-500</t>
-  </si>
-  <si>
-    <t>g_ID34-500-w265568001-500</t>
-  </si>
-  <si>
-    <t>e_ID36-500</t>
-  </si>
-  <si>
-    <t>e_w265318414-500</t>
-  </si>
-  <si>
-    <t>g_ID36-500-w265318414-500</t>
-  </si>
-  <si>
-    <t>e_ID4-275</t>
-  </si>
-  <si>
-    <t>e_ID3-275</t>
-  </si>
-  <si>
-    <t>g_ID4-275-ID3-275</t>
-  </si>
-  <si>
-    <t>e_ID5-275</t>
-  </si>
-  <si>
-    <t>e_w928928133-275</t>
-  </si>
-  <si>
-    <t>g_ID5-275-w928928133-275</t>
-  </si>
-  <si>
-    <t>e_ID6-275</t>
-  </si>
-  <si>
-    <t>g_ID6-275-w928928133-275</t>
-  </si>
-  <si>
-    <t>e_ID7-275</t>
-  </si>
-  <si>
-    <t>e_w930719092-275</t>
-  </si>
-  <si>
-    <t>g_ID7-275-w930719092-275</t>
-  </si>
-  <si>
-    <t>e_w939542521-275</t>
-  </si>
-  <si>
-    <t>g_ID7-275-w939542521-275</t>
-  </si>
-  <si>
-    <t>e_ID8-275</t>
-  </si>
-  <si>
-    <t>e_w1316786278-275</t>
-  </si>
-  <si>
-    <t>g_ID8-275-w1316786278-275</t>
-  </si>
-  <si>
-    <t>e_w1013653012-500</t>
-  </si>
-  <si>
-    <t>e_w960747936-500</t>
-  </si>
-  <si>
-    <t>g_w1013653012-500-w960747936-500</t>
-  </si>
-  <si>
-    <t>e_w1308433899-500</t>
-  </si>
-  <si>
-    <t>g_w1308433899-500-ID36-500</t>
-  </si>
-  <si>
-    <t>e_w1312287191-275</t>
-  </si>
-  <si>
-    <t>g_w1312287191-275-ID7-275</t>
-  </si>
-  <si>
-    <t>e_w159940153-500</t>
-  </si>
-  <si>
-    <t>g_w159940153-500-ID16-500</t>
-  </si>
-  <si>
-    <t>e_w161960924-500</t>
-  </si>
-  <si>
-    <t>g_w161960924-500-ID33-500</t>
-  </si>
-  <si>
-    <t>e_w966209515-500</t>
-  </si>
-  <si>
-    <t>g_w161960924-500-w966209515-500</t>
-  </si>
-  <si>
-    <t>e_w161960933-500</t>
-  </si>
-  <si>
-    <t>g_w161960933-500-w161960924-500</t>
-  </si>
-  <si>
-    <t>e_w399038181-500</t>
-  </si>
-  <si>
-    <t>g_w161960933-500-w399038181-500</t>
-  </si>
-  <si>
-    <t>e_w161965853-500</t>
-  </si>
-  <si>
-    <t>g_w161965853-500-ID11-500</t>
-  </si>
-  <si>
-    <t>g_w161965853-500-w966209515-500</t>
-  </si>
-  <si>
-    <t>g_w166633831-500-ID28-500</t>
-  </si>
-  <si>
-    <t>g_w166633831-500-w1308433899-500</t>
-  </si>
-  <si>
-    <t>g_w166633831-500-w265568001-500</t>
-  </si>
-  <si>
-    <t>e_w398909640-500</t>
-  </si>
-  <si>
-    <t>g_w166633831-500-w398909640-500</t>
-  </si>
-  <si>
-    <t>e_w169444592-500</t>
-  </si>
-  <si>
-    <t>g_w169444592-500-ID11-500</t>
-  </si>
-  <si>
-    <t>g_w169444592-500-ID12-500</t>
-  </si>
-  <si>
-    <t>g_w169444592-500-w399038181-500</t>
-  </si>
-  <si>
-    <t>e_w261185002-500</t>
-  </si>
-  <si>
-    <t>e_ID29-500</t>
-  </si>
-  <si>
-    <t>g_w261185002-500-ID29-500</t>
-  </si>
-  <si>
-    <t>g_w261185002-500-ID31-500</t>
-  </si>
-  <si>
-    <t>g_w261185002-500-w1013653012-500</t>
-  </si>
-  <si>
-    <t>g_w261185002-500-w689263666-500</t>
-  </si>
-  <si>
-    <t>g_w264410236-500-w261185002-500</t>
-  </si>
-  <si>
-    <t>e_w769617021-500</t>
-  </si>
-  <si>
-    <t>g_w264410236-500-w769617021-500</t>
-  </si>
-  <si>
-    <t>g_w264550744-500-w264410236-500</t>
-  </si>
-  <si>
-    <t>e_ID38-500</t>
-  </si>
-  <si>
-    <t>g_w265318414-500-ID38-500</t>
-  </si>
-  <si>
-    <t>e_w340978681-500</t>
-  </si>
-  <si>
-    <t>g_w265568001-500-w340978681-500</t>
-  </si>
-  <si>
-    <t>e_w267626657-500</t>
-  </si>
-  <si>
-    <t>g_w267626657-500-ID36-500</t>
-  </si>
-  <si>
-    <t>e_ID37-500</t>
-  </si>
-  <si>
-    <t>g_w267626657-500-ID37-500</t>
-  </si>
-  <si>
-    <t>g_w271376037-500-ID21-500</t>
-  </si>
-  <si>
-    <t>e_ID24-500</t>
-  </si>
-  <si>
-    <t>g_w271376037-500-ID24-500</t>
-  </si>
-  <si>
-    <t>e_w310958602-275</t>
-  </si>
-  <si>
-    <t>e_w754096394-275</t>
-  </si>
-  <si>
-    <t>g_w310958602-275-w754096394-275</t>
-  </si>
-  <si>
-    <t>g_w314452486-500-w267626657-500</t>
-  </si>
-  <si>
-    <t>e_w337039411-275</t>
-  </si>
-  <si>
-    <t>e_w310695690-275</t>
-  </si>
-  <si>
-    <t>g_w337039411-275-w310695690-275</t>
-  </si>
-  <si>
-    <t>e_w340205049-275</t>
-  </si>
-  <si>
-    <t>e_w754073846-275</t>
-  </si>
-  <si>
-    <t>g_w340205049-275-w754073846-275</t>
-  </si>
-  <si>
-    <t>g_w340205049-275-w754096394-275</t>
-  </si>
-  <si>
-    <t>e_ID35-500</t>
-  </si>
-  <si>
-    <t>g_w340978681-500-ID35-500</t>
-  </si>
-  <si>
-    <t>g_w340978681-500-ID38-500</t>
-  </si>
-  <si>
-    <t>g_w398909640-500-w265568001-500</t>
-  </si>
-  <si>
-    <t>g_w399038181-500-w662591948-500</t>
-  </si>
-  <si>
-    <t>e_w399100034-500</t>
-  </si>
-  <si>
-    <t>g_w399100034-500-w960747902-500</t>
-  </si>
-  <si>
-    <t>g_w399100034-500-w960747936-500</t>
-  </si>
-  <si>
-    <t>e_w399100035-500</t>
-  </si>
-  <si>
-    <t>g_w399100035-500-w264550744-500</t>
-  </si>
-  <si>
-    <t>e_w469888049-275</t>
-  </si>
-  <si>
-    <t>g_w469888049-275-w928928133-275</t>
-  </si>
-  <si>
-    <t>e_w527900241-275</t>
-  </si>
-  <si>
-    <t>e_w528189342-275</t>
-  </si>
-  <si>
-    <t>g_w527900241-275-w528189342-275</t>
-  </si>
-  <si>
-    <t>e_w931931133-275</t>
-  </si>
-  <si>
-    <t>g_w527900241-275-w931931133-275</t>
-  </si>
-  <si>
-    <t>e_w544403426-230</t>
-  </si>
-  <si>
-    <t>e_ID9-230</t>
-  </si>
-  <si>
-    <t>g_w544403426-230-ID9-230</t>
-  </si>
-  <si>
-    <t>e_w544403431-230</t>
-  </si>
-  <si>
-    <t>e_w759130125-230</t>
-  </si>
-  <si>
-    <t>g_w544403431-230-w759130125-230</t>
-  </si>
-  <si>
-    <t>e_w562061281-275</t>
-  </si>
-  <si>
-    <t>e_ID2-275</t>
-  </si>
-  <si>
-    <t>g_w562061281-275-ID2-275</t>
-  </si>
-  <si>
-    <t>e_w604684007-500</t>
-  </si>
-  <si>
-    <t>g_w604684007-500-w161960933-500</t>
-  </si>
-  <si>
-    <t>g_w604684007-500-w169444592-500</t>
-  </si>
-  <si>
-    <t>e_w614955990-230</t>
-  </si>
-  <si>
-    <t>g_w614955990-230-ID9-230</t>
-  </si>
-  <si>
-    <t>e_w614955993-230</t>
-  </si>
-  <si>
-    <t>g_w614955993-230-w544403431-230</t>
-  </si>
-  <si>
-    <t>g_w614955993-230-w614955990-230</t>
-  </si>
-  <si>
-    <t>e_w615581232-275</t>
-  </si>
-  <si>
-    <t>e_w615581242-275</t>
-  </si>
-  <si>
-    <t>g_w615581232-275-w615581242-275</t>
-  </si>
-  <si>
-    <t>e_w1193553154-275</t>
-  </si>
-  <si>
-    <t>g_w615581242-275-w1193553154-275</t>
-  </si>
-  <si>
-    <t>e_w615581270-275</t>
-  </si>
-  <si>
-    <t>g_w615581270-275-w615581232-275</t>
-  </si>
-  <si>
-    <t>e_w629512849-500</t>
-  </si>
-  <si>
-    <t>g_w629512849-500-ID37-500</t>
-  </si>
-  <si>
-    <t>e_ID15-500</t>
-  </si>
-  <si>
-    <t>g_w662591948-500-ID15-500</t>
-  </si>
-  <si>
-    <t>g_w689263666-500-ID27-500</t>
-  </si>
-  <si>
-    <t>e_ID30-500</t>
-  </si>
-  <si>
-    <t>g_w689263666-500-ID30-500</t>
-  </si>
-  <si>
-    <t>g_w689263666-500-ID31-500</t>
-  </si>
-  <si>
-    <t>e_w721674155-275</t>
-  </si>
-  <si>
-    <t>g_w721674155-275-w310958602-275</t>
-  </si>
-  <si>
-    <t>g_w721674155-275-w469888049-275</t>
-  </si>
-  <si>
-    <t>e_w736595653-275</t>
-  </si>
-  <si>
-    <t>g_w736595653-275-ID3-275</t>
-  </si>
-  <si>
-    <t>e_w736595653-500</t>
-  </si>
-  <si>
-    <t>e_w1186182648-500</t>
-  </si>
-  <si>
-    <t>g_w736595653-500-w1186182648-500</t>
-  </si>
-  <si>
-    <t>e_w753733608-275</t>
-  </si>
-  <si>
-    <t>e_w610198177-275</t>
-  </si>
-  <si>
-    <t>g_w753733608-275-w610198177-275</t>
-  </si>
-  <si>
-    <t>e_w754178666-275</t>
-  </si>
-  <si>
-    <t>g_w754178666-275-w310695690-275</t>
-  </si>
-  <si>
-    <t>e_w754178667-275</t>
-  </si>
-  <si>
-    <t>g_w754178667-275-w310958602-275</t>
-  </si>
-  <si>
-    <t>g_w769617021-500-w261185002-500</t>
-  </si>
-  <si>
-    <t>e_w841499143-275</t>
-  </si>
-  <si>
-    <t>g_w841499143-275-w528189342-275</t>
-  </si>
-  <si>
-    <t>g_w841499143-275-w930719092-275</t>
-  </si>
-  <si>
-    <t>e_w926254403-500</t>
-  </si>
-  <si>
-    <t>g_w926254403-500-ID25-500</t>
-  </si>
-  <si>
-    <t>e_w928220391-275</t>
-  </si>
-  <si>
-    <t>g_w928220391-275-w721685825-275</t>
-  </si>
-  <si>
-    <t>g_w928928133-275-w939542521-275</t>
-  </si>
-  <si>
-    <t>e_w931931121-275</t>
-  </si>
-  <si>
-    <t>g_w931931121-275-w1316786278-275</t>
-  </si>
-  <si>
-    <t>e_w1316876158-275</t>
-  </si>
-  <si>
-    <t>g_w931931121-275-w1316876158-275</t>
-  </si>
-  <si>
-    <t>g_w931931133-275-w1316786278-275</t>
-  </si>
-  <si>
-    <t>e_w943539373-275</t>
-  </si>
-  <si>
-    <t>e_w946191122-275</t>
-  </si>
-  <si>
-    <t>g_w943539373-275-w946191122-275</t>
-  </si>
-  <si>
-    <t>e_w943539373-500</t>
-  </si>
-  <si>
-    <t>g_w943539373-500-w1186182648-500</t>
-  </si>
-  <si>
-    <t>g_w946191122-275-w753733608-275</t>
-  </si>
-  <si>
-    <t>e_ID23-500</t>
-  </si>
-  <si>
-    <t>g_w960747902-500-ID23-500</t>
-  </si>
-  <si>
-    <t>g_w960747936-500-w399100035-500</t>
-  </si>
-  <si>
-    <t>g_w966209515-500-ID26-500</t>
-  </si>
-  <si>
-    <t>g_w966209515-500-w926254403-500</t>
+    <t>e_ID11-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID10-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID11-500_IDN-ID10-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID12-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID12-500_IDN-ID10-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID13-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID16-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID13-500_IDN-ID16-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID22-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID13-500_IDN-ID22-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w960747902-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID13-500_IDN-w960747902-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID14-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID17-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID14-500_IDN-ID17-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID19-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID16-500_IDN-ID19-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID18-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w662591948-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID18-500_IDN-w662591948-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID20-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID20-500_IDN-ID19-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID21-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID21-500_IDN-ID20-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID25-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID22-500_IDN-ID25-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w271376037-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID22-500_IDN-w271376037-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID26-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w264550744-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID26-500_IDN-w264550744-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID27-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID28-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID27-500_IDN-ID28-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID31-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w166633831-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID31-500_IDN-w166633831-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w689263666-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID31-500_IDN-w689263666-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID33-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w264410236-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID33-500_IDN-w264410236-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w314452486-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID33-500_IDN-w314452486-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID34-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w265568001-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID34-500_IDN-w265568001-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID36-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w265318414-500_IDN</t>
+  </si>
+  <si>
+    <t>g_ID36-500_IDN-w265318414-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID4-275_IDN</t>
+  </si>
+  <si>
+    <t>e_ID3-275_IDN</t>
+  </si>
+  <si>
+    <t>g_ID4-275_IDN-ID3-275_IDN</t>
+  </si>
+  <si>
+    <t>e_ID5-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w928928133-275_IDN</t>
+  </si>
+  <si>
+    <t>g_ID5-275_IDN-w928928133-275_IDN</t>
+  </si>
+  <si>
+    <t>e_ID6-275_IDN</t>
+  </si>
+  <si>
+    <t>g_ID6-275_IDN-w928928133-275_IDN</t>
+  </si>
+  <si>
+    <t>e_ID7-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w930719092-275_IDN</t>
+  </si>
+  <si>
+    <t>g_ID7-275_IDN-w930719092-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w939542521-275_IDN</t>
+  </si>
+  <si>
+    <t>g_ID7-275_IDN-w939542521-275_IDN</t>
+  </si>
+  <si>
+    <t>e_ID8-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w1316786278-275_IDN</t>
+  </si>
+  <si>
+    <t>g_ID8-275_IDN-w1316786278-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w1013653012-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w960747936-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w1013653012-500_IDN-w960747936-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w1308433899-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w1308433899-500_IDN-ID36-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w1312287191-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w1312287191-275_IDN-ID7-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w159940153-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w159940153-500_IDN-ID16-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w161960924-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w161960924-500_IDN-ID33-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w966209515-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w161960924-500_IDN-w966209515-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w161960933-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w161960933-500_IDN-w161960924-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w399038181-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w161960933-500_IDN-w399038181-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w161965853-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w161965853-500_IDN-ID11-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w161965853-500_IDN-w966209515-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w166633831-500_IDN-ID28-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w166633831-500_IDN-w1308433899-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w166633831-500_IDN-w265568001-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w398909640-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w166633831-500_IDN-w398909640-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w169444592-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w169444592-500_IDN-ID11-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w169444592-500_IDN-ID12-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w169444592-500_IDN-w399038181-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w261185002-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID29-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w261185002-500_IDN-ID29-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w261185002-500_IDN-ID31-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w261185002-500_IDN-w1013653012-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w261185002-500_IDN-w689263666-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w264410236-500_IDN-w261185002-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w769617021-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w264410236-500_IDN-w769617021-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w264550744-500_IDN-w264410236-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w265318414-500_IDN-ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w340978681-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w265568001-500_IDN-w340978681-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w267626657-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w267626657-500_IDN-ID36-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID37-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w267626657-500_IDN-ID37-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w271376037-500_IDN-ID21-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID24-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w271376037-500_IDN-ID24-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w310958602-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w754096394-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w310958602-275_IDN-w754096394-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w314452486-500_IDN-w267626657-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w337039411-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w310695690-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w337039411-275_IDN-w310695690-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w340205049-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w754073846-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w340205049-275_IDN-w754073846-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w340205049-275_IDN-w754096394-275_IDN</t>
+  </si>
+  <si>
+    <t>e_ID35-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w340978681-500_IDN-ID35-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w340978681-500_IDN-ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w398909640-500_IDN-w265568001-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w399038181-500_IDN-w662591948-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w399100034-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w399100034-500_IDN-w960747902-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w399100034-500_IDN-w960747936-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w399100035-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w399100035-500_IDN-w264550744-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w469888049-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w469888049-275_IDN-w928928133-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w527900241-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w528189342-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w527900241-275_IDN-w528189342-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w931931133-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w527900241-275_IDN-w931931133-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w544403426-230_IDN</t>
+  </si>
+  <si>
+    <t>e_ID9-230_IDN</t>
+  </si>
+  <si>
+    <t>g_w544403426-230_IDN-ID9-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w544403431-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w759130125-230_IDN</t>
+  </si>
+  <si>
+    <t>g_w544403431-230_IDN-w759130125-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w562061281-275_IDN</t>
+  </si>
+  <si>
+    <t>e_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w562061281-275_IDN-ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w604684007-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w604684007-500_IDN-w161960933-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w604684007-500_IDN-w169444592-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w614955990-230_IDN</t>
+  </si>
+  <si>
+    <t>g_w614955990-230_IDN-ID9-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w614955993-230_IDN</t>
+  </si>
+  <si>
+    <t>g_w614955993-230_IDN-w544403431-230_IDN</t>
+  </si>
+  <si>
+    <t>g_w614955993-230_IDN-w614955990-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w615581232-275_IDN-w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w1193553154-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w615581242-275_IDN-w1193553154-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w615581270-275_IDN-w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w629512849-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w629512849-500_IDN-ID37-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID15-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w662591948-500_IDN-ID15-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w689263666-500_IDN-ID27-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID30-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w689263666-500_IDN-ID30-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w689263666-500_IDN-ID31-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w721674155-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w721674155-275_IDN-w310958602-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w721674155-275_IDN-w469888049-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w736595653-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w736595653-275_IDN-ID3-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w736595653-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w1186182648-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w736595653-500_IDN-w1186182648-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w753733608-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w610198177-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w753733608-275_IDN-w610198177-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w754178666-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w754178666-275_IDN-w310695690-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w754178667-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w754178667-275_IDN-w310958602-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w769617021-500_IDN-w261185002-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w841499143-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w841499143-275_IDN-w528189342-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w841499143-275_IDN-w930719092-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w926254403-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w926254403-500_IDN-ID25-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w928220391-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w928220391-275_IDN-w721685825-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w928928133-275_IDN-w939542521-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w931931121-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w931931121-275_IDN-w1316786278-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w1316876158-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w931931121-275_IDN-w1316876158-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w931931133-275_IDN-w1316786278-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w943539373-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w946191122-275_IDN</t>
+  </si>
+  <si>
+    <t>g_w943539373-275_IDN-w946191122-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w943539373-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w943539373-500_IDN-w1186182648-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w946191122-275_IDN-w753733608-275_IDN</t>
+  </si>
+  <si>
+    <t>e_ID23-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w960747902-500_IDN-ID23-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w960747936-500_IDN-w399100035-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w966209515-500_IDN-ID26-500_IDN</t>
+  </si>
+  <si>
+    <t>g_w966209515-500_IDN-w926254403-500_IDN</t>
   </si>
   <si>
     <t>~tradelinks_desc</t>
@@ -1360,7 +1363,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD39DA5-6911-4B79-8860-B4723B99D995}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30C9E78B-792C-4182-BDEB-C0E6126D3309}">
   <dimension ref="B3:L115"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_IDN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A92EE9EC-722D-4252-97D9-B47A16758D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{82A55F28-A6A1-4F21-9B3F-B077E78EE62E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0D89265B-3111-4EDC-B670-7EC3D7D3C691}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{97342B96-7FDB-4D33-B2B9-982F42BE4DBA}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1003,7 +1003,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1058,39 +1058,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1142,7 +1142,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1253,6 +1253,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -1261,13 +1268,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1332,38 +1332,18 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30C9E78B-792C-4182-BDEB-C0E6126D3309}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9158F265-0271-440E-91F8-1413D0FCACDE}">
   <dimension ref="B3:L115"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_IDN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{82A55F28-A6A1-4F21-9B3F-B077E78EE62E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1B816F1-16B4-4BF6-A85A-5F97BBB89000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{97342B96-7FDB-4D33-B2B9-982F42BE4DBA}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{7B35EF97-683B-41F7-B55B-FCB303341DA1}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1343,7 +1343,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9158F265-0271-440E-91F8-1413D0FCACDE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F7C12FB-C156-4ABD-BC68-55775B85FA38}">
   <dimension ref="B3:L115"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
